--- a/Usage/Output/sparse_FanIn.xlsx
+++ b/Usage/Output/sparse_FanIn.xlsx
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>115553</v>
+        <v>115852</v>
       </c>
       <c r="D5" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E5" t="n">
         <v>27</v>
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>61564</v>
+        <v>61678</v>
       </c>
       <c r="D7" t="n">
-        <v>61564</v>
+        <v>61678</v>
       </c>
       <c r="E7" t="n">
         <v>8</v>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56301</v>
+        <v>56185</v>
       </c>
       <c r="D8" t="n">
         <v>1249</v>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14487</v>
+        <v>14306</v>
       </c>
       <c r="D13" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" t="n">
         <v>34</v>
@@ -1867,7 +1867,7 @@
         <v>120</v>
       </c>
       <c r="D56" t="n">
-        <v>761427</v>
+        <v>761402</v>
       </c>
       <c r="E56" t="n">
         <v>3</v>
